--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,10 +37,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="007D3C00"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD580"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,10 +102,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -473,6 +486,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -506,6 +530,61 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -523,24 +602,79 @@
           <t>IDFCFIRSTB</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>LODHA</t>
         </is>
@@ -550,7 +684,7 @@
           <t>NYKAA</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>PETRONET</t>
         </is>
@@ -568,6 +702,61 @@
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
@@ -582,17 +771,17 @@
           <t>AUBANK</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OIL</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
@@ -602,9 +791,64 @@
           <t>POLICYBZR</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -632,6 +876,61 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -641,17 +940,17 @@
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>SOLARINDS</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
@@ -661,9 +960,64 @@
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>GAIL</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
         </is>
       </c>
     </row>
@@ -673,7 +1027,7 @@
           <t>NYKAA</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
@@ -693,14 +1047,69 @@
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SOLARINDS</t>
         </is>
@@ -725,19 +1134,74 @@
           <t>CDSL</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
       </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>PNBHOUSING</t>
         </is>
@@ -752,14 +1216,65 @@
           <t>DLF</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
@@ -769,7 +1284,7 @@
           <t>NMDC</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -779,7 +1294,7 @@
           <t>CGPOWER</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
         </is>
@@ -794,19 +1309,70 @@
           <t>NYKAA</t>
         </is>
       </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>JINDALSTEL</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -816,7 +1382,7 @@
           <t>GRASIM</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>SOLARINDS</t>
         </is>
@@ -824,6 +1390,53 @@
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -833,12 +1446,12 @@
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
         </is>
@@ -848,7 +1461,7 @@
           <t>BHEL</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
         </is>
@@ -858,36 +1471,122 @@
           <t>CGPOWER</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>NMDC</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>INDIANB</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
         </is>
       </c>
     </row>
@@ -902,7 +1601,7 @@
           <t>UNOMINDA</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -912,19 +1611,58 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>OIL</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
       </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
@@ -934,29 +1672,64 @@
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>RBLBANK</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>APLAPOLLO</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ZYDUSLIFE</t>
         </is>
@@ -986,30 +1759,76 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>HYUNDAI</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LODHA</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>CGPOWER</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1022,7 +1841,7 @@
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -1032,16 +1851,27 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
@@ -1051,13 +1881,24 @@
           <t>DLF</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1070,7 +1911,7 @@
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
@@ -1080,11 +1921,22 @@
           <t>CDSL</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>SAGILITY</t>
         </is>
@@ -1094,7 +1946,7 @@
           <t>POLICYBZR</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>TORNTPHARM</t>
         </is>
@@ -1104,8 +1956,19 @@
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1119,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1128,6 +1991,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1161,6 +2035,61 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1168,7 +2097,7 @@
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CAMS</t>
         </is>
@@ -1188,46 +2117,156 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>DELHIVERY</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SONACOMS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>CDSL</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>CDSL</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>NATIONALUM</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>CAMS</t>
         </is>
@@ -1247,7 +2286,7 @@
           <t>HINDZINC</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DELHIVERY</t>
         </is>
@@ -1257,14 +2296,69 @@
           <t>MAZDOCK</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
@@ -1274,7 +2368,7 @@
           <t>PETRONET</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>MAZDOCK</t>
         </is>
@@ -1284,9 +2378,64 @@
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
@@ -1306,7 +2455,7 @@
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -1321,29 +2470,84 @@
           <t>PREMIERENE</t>
         </is>
       </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>AUBANK</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>NMDC</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
@@ -1351,6 +2555,61 @@
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
@@ -1360,7 +2619,7 @@
           <t>MANKIND</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>DELHIVERY</t>
         </is>
@@ -1385,36 +2644,146 @@
           <t>NESTLEIND</t>
         </is>
       </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>HAL</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
         </is>
       </c>
     </row>
@@ -1439,7 +2808,7 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>PETRONET</t>
         </is>
@@ -1449,19 +2818,74 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>NAM-INDIA</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>NMDC</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>ZYDUSLIFE</t>
         </is>
@@ -1471,12 +2895,67 @@
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>NAM-INDIA</t>
         </is>
@@ -1498,7 +2977,7 @@
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
@@ -1508,9 +2987,64 @@
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
@@ -1520,12 +3054,12 @@
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>MAZDOCK</t>
         </is>
@@ -1535,14 +3069,69 @@
           <t>DELHIVERY</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>PGEL</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>CDSL</t>
         </is>
       </c>
     </row>
@@ -1572,19 +3161,74 @@
           <t>LODHA</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>MARICO</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1594,7 +3238,7 @@
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ADANIGREEN</t>
         </is>
@@ -1604,9 +3248,64 @@
           <t>AMBER</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
         </is>
       </c>
     </row>
@@ -1621,7 +3320,7 @@
           <t>MPHASIS</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>DELHIVERY</t>
         </is>
@@ -1641,30 +3340,96 @@
           <t>CDSL</t>
         </is>
       </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>NATIONALUM</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1687,11 +3452,22 @@
           <t>MANAPPURAM</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>IEX</t>
         </is>
@@ -1706,13 +3482,24 @@
           <t>AMBER</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>GODREJPROP</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1730,21 +3517,32 @@
           <t>LODHA</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>PETRONET</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>BHARATFORG</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -1754,13 +3552,24 @@
           <t>CAMS</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1774,7 +3583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1783,6 +3592,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1816,6 +3636,61 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1823,22 +3698,22 @@
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1848,14 +3723,69 @@
           <t>APOLLOHOSP</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1875,11 +3805,46 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>SIEMENS</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1907,14 +3872,41 @@
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
@@ -1944,6 +3936,29 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,17 +3971,17 @@
           <t>SBIN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -1976,14 +3991,33 @@
           <t>UNIONBANK</t>
         </is>
       </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>LTF</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
@@ -2003,7 +4037,22 @@
           <t>ABB</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2026,15 +4075,26 @@
           <t>SIEMENS</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>UNOMINDA</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
         </is>
@@ -2059,7 +4119,18 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2067,17 +4138,17 @@
           <t>INDIANB</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>UNOMINDA</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNOMINDA</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>PNBHOUSING</t>
         </is>
@@ -2087,7 +4158,18 @@
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2095,7 +4177,7 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>360ONE</t>
         </is>
@@ -2110,11 +4192,22 @@
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
@@ -2134,11 +4227,22 @@
           <t>NAUKRI</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>RBLBANK</t>
         </is>
@@ -2148,14 +4252,25 @@
           <t>PNB</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>NAUKRI</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2168,10 +4283,21 @@
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2184,10 +4310,21 @@
           <t>TITAN</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2200,26 +4337,48 @@
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>RBLBANK</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2232,13 +4391,24 @@
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SUPREMEIND</t>
         </is>
@@ -2248,13 +4418,24 @@
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2264,10 +4445,21 @@
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2275,15 +4467,26 @@
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,6 +497,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -585,6 +597,66 @@
           <t>2026-09-24</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -667,9 +739,69 @@
           <t>PNB</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>MCX</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
         </is>
       </c>
     </row>
@@ -759,6 +891,66 @@
           <t>MOTHERSON</t>
         </is>
       </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -836,14 +1028,74 @@
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>SONACOMS</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
@@ -933,6 +1185,62 @@
           <t>ZYDUSLIFE</t>
         </is>
       </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1020,6 +1328,62 @@
           <t>DIVISLAB</t>
         </is>
       </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1107,6 +1471,58 @@
           <t>MOTILALOFS</t>
         </is>
       </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1194,6 +1610,54 @@
           <t>MAHABANK</t>
         </is>
       </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1277,6 +1741,46 @@
           <t>ETERNAL</t>
         </is>
       </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1360,6 +1864,46 @@
           <t>LICHSGFIN</t>
         </is>
       </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1434,9 +1978,49 @@
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
@@ -1513,9 +2097,49 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>DLF</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -1589,6 +2213,46 @@
           <t>MANKIND</t>
         </is>
       </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1658,6 +2322,42 @@
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr"/>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
         </is>
       </c>
     </row>
@@ -1717,7 +2417,7 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
@@ -1725,6 +2425,38 @@
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr"/>
+      <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
@@ -1784,7 +2516,7 @@
           <t>PAYTM</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>RBLBANK</t>
         </is>
@@ -1792,6 +2524,38 @@
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -1829,6 +2593,18 @@
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="AA17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AC17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1864,6 +2640,18 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="AA18" s="5" t="inlineStr"/>
+      <c r="AB18" s="5" t="inlineStr"/>
+      <c r="AC18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1899,6 +2687,18 @@
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="AA19" s="5" t="inlineStr"/>
+      <c r="AB19" s="5" t="inlineStr"/>
+      <c r="AC19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1934,6 +2734,18 @@
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
       <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="5" t="inlineStr"/>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="5" t="inlineStr"/>
+      <c r="AB20" s="5" t="inlineStr"/>
+      <c r="AC20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1969,6 +2781,18 @@
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1982,7 +2806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2002,6 +2826,17 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2090,6 +2925,61 @@
           <t>2026-09-24</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2172,9 +3062,64 @@
           <t>MANAPPURAM</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>OIL</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
@@ -2259,9 +3204,64 @@
           <t>ANGELONE</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
@@ -2351,6 +3351,61 @@
           <t>MAHABANK</t>
         </is>
       </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2438,6 +3493,61 @@
           <t>KOTAKBANK</t>
         </is>
       </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2525,6 +3635,61 @@
           <t>ABB</t>
         </is>
       </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2612,6 +3777,61 @@
           <t>HINDZINC</t>
         </is>
       </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2699,6 +3919,61 @@
           <t>BOSCHLTD</t>
         </is>
       </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2781,9 +4056,64 @@
           <t>POLYCAB</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>UJJIVANSFB</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
         </is>
       </c>
     </row>
@@ -2873,6 +4203,61 @@
           <t>MANAPPURAM</t>
         </is>
       </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2960,6 +4345,61 @@
           <t>NAM-INDIA</t>
         </is>
       </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3037,7 +4477,7 @@
           <t>POLYCAB</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
@@ -3045,6 +4485,61 @@
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
@@ -3134,6 +4629,61 @@
           <t>CDSL</t>
         </is>
       </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3221,6 +4771,61 @@
           <t>TVSMOTOR</t>
         </is>
       </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3308,6 +4913,61 @@
           <t>SIEMENS</t>
         </is>
       </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>UJJIVANSFB</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3393,6 +5053,61 @@
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
@@ -3430,6 +5145,17 @@
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="AA17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3465,6 +5191,17 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="AA18" s="5" t="inlineStr"/>
+      <c r="AB18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3500,6 +5237,17 @@
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="AA19" s="5" t="inlineStr"/>
+      <c r="AB19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3535,6 +5283,17 @@
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
       <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="5" t="inlineStr"/>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="5" t="inlineStr"/>
+      <c r="AB20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3570,6 +5329,17 @@
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3583,7 +5353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3603,6 +5373,12 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3691,6 +5467,36 @@
           <t>2026-09-24</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3776,6 +5582,36 @@
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>
@@ -3845,6 +5681,12 @@
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3904,6 +5746,12 @@
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3959,6 +5807,12 @@
       <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4010,6 +5864,12 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4053,6 +5913,12 @@
       <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4092,6 +5958,12 @@
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4131,6 +6003,12 @@
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4170,6 +6048,12 @@
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4205,6 +6089,12 @@
       <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4240,6 +6130,12 @@
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr"/>
+      <c r="W12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4271,6 +6167,12 @@
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4298,6 +6200,12 @@
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr"/>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4325,6 +6233,12 @@
       <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr"/>
+      <c r="W15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4352,6 +6266,12 @@
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4379,6 +6299,12 @@
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4406,6 +6332,12 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4433,6 +6365,12 @@
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4460,6 +6398,12 @@
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
       <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="5" t="inlineStr"/>
+      <c r="W20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4487,6 +6431,12 @@
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Analysis/exports/consolidated_history.xlsx
+++ b/Analysis/exports/consolidated_history.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -509,6 +509,13 @@
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -657,6 +664,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -799,9 +841,44 @@
           <t>ANGELONE</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
@@ -951,6 +1028,41 @@
           <t>LAURUSLABS</t>
         </is>
       </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1088,7 +1200,7 @@
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>NYKAA</t>
         </is>
@@ -1096,6 +1208,41 @@
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
         </is>
       </c>
     </row>
@@ -1241,6 +1388,37 @@
           <t>DLF</t>
         </is>
       </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="AH5" s="5" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1379,9 +1557,32 @@
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AG6" s="5" t="inlineStr"/>
+      <c r="AH6" s="5" t="inlineStr"/>
+      <c r="AI6" s="5" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1714,7 @@
           <t>ANGELONE</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>INDHOTEL</t>
         </is>
@@ -1521,6 +1722,29 @@
       <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="inlineStr"/>
+      <c r="AH7" s="5" t="inlineStr"/>
+      <c r="AI7" s="5" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
@@ -1658,6 +1882,29 @@
           <t>FEDERALBNK</t>
         </is>
       </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="AG8" s="5" t="inlineStr"/>
+      <c r="AH8" s="5" t="inlineStr"/>
+      <c r="AI8" s="5" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1771,7 +2018,7 @@
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>MOTILALOFS</t>
         </is>
@@ -1779,6 +2026,21 @@
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="AE9" s="5" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr"/>
+      <c r="AG9" s="5" t="inlineStr"/>
+      <c r="AH9" s="5" t="inlineStr"/>
+      <c r="AI9" s="5" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -1899,11 +2161,22 @@
           <t>PETRONET</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>INDHOTEL</t>
         </is>
       </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AE10" s="5" t="inlineStr"/>
+      <c r="AF10" s="5" t="inlineStr"/>
+      <c r="AG10" s="5" t="inlineStr"/>
+      <c r="AH10" s="5" t="inlineStr"/>
+      <c r="AI10" s="5" t="inlineStr"/>
+      <c r="AJ10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2023,6 +2296,17 @@
           <t>BHEL</t>
         </is>
       </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr"/>
+      <c r="AG11" s="5" t="inlineStr"/>
+      <c r="AH11" s="5" t="inlineStr"/>
+      <c r="AI11" s="5" t="inlineStr"/>
+      <c r="AJ11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2142,6 +2426,17 @@
           <t>PIDILITIND</t>
         </is>
       </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr"/>
+      <c r="AG12" s="5" t="inlineStr"/>
+      <c r="AH12" s="5" t="inlineStr"/>
+      <c r="AI12" s="5" t="inlineStr"/>
+      <c r="AJ12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2253,6 +2548,17 @@
           <t>ADANIENSOL</t>
         </is>
       </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr"/>
+      <c r="AG13" s="5" t="inlineStr"/>
+      <c r="AH13" s="5" t="inlineStr"/>
+      <c r="AI13" s="5" t="inlineStr"/>
+      <c r="AJ13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2360,6 +2666,17 @@
           <t>RADICO</t>
         </is>
       </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr"/>
+      <c r="AF14" s="5" t="inlineStr"/>
+      <c r="AG14" s="5" t="inlineStr"/>
+      <c r="AH14" s="5" t="inlineStr"/>
+      <c r="AI14" s="5" t="inlineStr"/>
+      <c r="AJ14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2459,6 +2776,17 @@
           <t>SOLARINDS</t>
         </is>
       </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr"/>
+      <c r="AF15" s="5" t="inlineStr"/>
+      <c r="AG15" s="5" t="inlineStr"/>
+      <c r="AH15" s="5" t="inlineStr"/>
+      <c r="AI15" s="5" t="inlineStr"/>
+      <c r="AJ15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2558,6 +2886,17 @@
           <t>PNBHOUSING</t>
         </is>
       </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="AE16" s="5" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr"/>
+      <c r="AG16" s="5" t="inlineStr"/>
+      <c r="AH16" s="5" t="inlineStr"/>
+      <c r="AI16" s="5" t="inlineStr"/>
+      <c r="AJ16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2605,6 +2944,13 @@
       <c r="AA17" s="5" t="inlineStr"/>
       <c r="AB17" s="5" t="inlineStr"/>
       <c r="AC17" s="5" t="inlineStr"/>
+      <c r="AD17" s="5" t="inlineStr"/>
+      <c r="AE17" s="5" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr"/>
+      <c r="AG17" s="5" t="inlineStr"/>
+      <c r="AH17" s="5" t="inlineStr"/>
+      <c r="AI17" s="5" t="inlineStr"/>
+      <c r="AJ17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2652,6 +2998,13 @@
       <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="5" t="inlineStr"/>
       <c r="AC18" s="5" t="inlineStr"/>
+      <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AE18" s="5" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr"/>
+      <c r="AG18" s="5" t="inlineStr"/>
+      <c r="AH18" s="5" t="inlineStr"/>
+      <c r="AI18" s="5" t="inlineStr"/>
+      <c r="AJ18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2699,6 +3052,13 @@
       <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="5" t="inlineStr"/>
       <c r="AC19" s="5" t="inlineStr"/>
+      <c r="AD19" s="5" t="inlineStr"/>
+      <c r="AE19" s="5" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr"/>
+      <c r="AG19" s="5" t="inlineStr"/>
+      <c r="AH19" s="5" t="inlineStr"/>
+      <c r="AI19" s="5" t="inlineStr"/>
+      <c r="AJ19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2746,6 +3106,13 @@
       <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="5" t="inlineStr"/>
       <c r="AC20" s="5" t="inlineStr"/>
+      <c r="AD20" s="5" t="inlineStr"/>
+      <c r="AE20" s="5" t="inlineStr"/>
+      <c r="AF20" s="5" t="inlineStr"/>
+      <c r="AG20" s="5" t="inlineStr"/>
+      <c r="AH20" s="5" t="inlineStr"/>
+      <c r="AI20" s="5" t="inlineStr"/>
+      <c r="AJ20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2793,6 +3160,13 @@
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="5" t="inlineStr"/>
       <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AE21" s="5" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr"/>
+      <c r="AG21" s="5" t="inlineStr"/>
+      <c r="AH21" s="5" t="inlineStr"/>
+      <c r="AI21" s="5" t="inlineStr"/>
+      <c r="AJ21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2806,7 +3180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2837,6 +3211,13 @@
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2980,6 +3361,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3117,9 +3533,44 @@
           <t>GLENMARK</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
@@ -3259,9 +3710,44 @@
           <t>IDFCFIRSTB</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>SAIL</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
@@ -3406,6 +3892,41 @@
           <t>PNB</t>
         </is>
       </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3548,6 +4069,41 @@
           <t>MANAPPURAM</t>
         </is>
       </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3690,6 +4246,41 @@
           <t>GLENMARK</t>
         </is>
       </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3832,6 +4423,41 @@
           <t>OBEROIRLTY</t>
         </is>
       </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3964,14 +4590,49 @@
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -4116,6 +4777,41 @@
           <t>ANANDRATHI</t>
         </is>
       </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4258,6 +4954,41 @@
           <t>ADANIENSOL</t>
         </is>
       </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4400,6 +5131,41 @@
           <t>BAJFINANCE</t>
         </is>
       </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AF11" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4542,6 +5308,41 @@
           <t>ABCAPITAL</t>
         </is>
       </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4684,6 +5485,41 @@
           <t>TITAN</t>
         </is>
       </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="AF13" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4826,6 +5662,41 @@
           <t>KALYANKJIL</t>
         </is>
       </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4958,14 +5829,49 @@
           <t>APLAPOLLO</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>UNITDSPR</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
         </is>
       </c>
     </row>
@@ -5108,6 +6014,41 @@
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
@@ -5156,6 +6097,13 @@
       <c r="Z17" s="5" t="inlineStr"/>
       <c r="AA17" s="5" t="inlineStr"/>
       <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AC17" s="5" t="inlineStr"/>
+      <c r="AD17" s="5" t="inlineStr"/>
+      <c r="AE17" s="5" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr"/>
+      <c r="AG17" s="5" t="inlineStr"/>
+      <c r="AH17" s="5" t="inlineStr"/>
+      <c r="AI17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5202,6 +6150,13 @@
       <c r="Z18" s="5" t="inlineStr"/>
       <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="5" t="inlineStr"/>
+      <c r="AC18" s="5" t="inlineStr"/>
+      <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AE18" s="5" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr"/>
+      <c r="AG18" s="5" t="inlineStr"/>
+      <c r="AH18" s="5" t="inlineStr"/>
+      <c r="AI18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5248,6 +6203,13 @@
       <c r="Z19" s="5" t="inlineStr"/>
       <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="5" t="inlineStr"/>
+      <c r="AC19" s="5" t="inlineStr"/>
+      <c r="AD19" s="5" t="inlineStr"/>
+      <c r="AE19" s="5" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr"/>
+      <c r="AG19" s="5" t="inlineStr"/>
+      <c r="AH19" s="5" t="inlineStr"/>
+      <c r="AI19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5294,6 +6256,13 @@
       <c r="Z20" s="5" t="inlineStr"/>
       <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="5" t="inlineStr"/>
+      <c r="AC20" s="5" t="inlineStr"/>
+      <c r="AD20" s="5" t="inlineStr"/>
+      <c r="AE20" s="5" t="inlineStr"/>
+      <c r="AF20" s="5" t="inlineStr"/>
+      <c r="AG20" s="5" t="inlineStr"/>
+      <c r="AH20" s="5" t="inlineStr"/>
+      <c r="AI20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -5340,6 +6309,13 @@
       <c r="Z21" s="5" t="inlineStr"/>
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AE21" s="5" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr"/>
+      <c r="AG21" s="5" t="inlineStr"/>
+      <c r="AH21" s="5" t="inlineStr"/>
+      <c r="AI21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5353,7 +6329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5379,6 +6355,8 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5497,6 +6475,16 @@
           <t>2026-10-15</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5612,6 +6600,16 @@
       <c r="W2" s="2" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
         </is>
       </c>
     </row>
@@ -5687,6 +6685,8 @@
       <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
       <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5752,6 +6752,8 @@
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5813,6 +6815,8 @@
       <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
       <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5870,6 +6874,8 @@
       <c r="U6" s="5" t="inlineStr"/>
       <c r="V6" s="5" t="inlineStr"/>
       <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5919,6 +6925,8 @@
       <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="5" t="inlineStr"/>
       <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5964,6 +6972,8 @@
       <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="5" t="inlineStr"/>
       <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6009,6 +7019,8 @@
       <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
       <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6054,6 +7066,8 @@
       <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="5" t="inlineStr"/>
       <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6095,6 +7109,8 @@
       <c r="U11" s="5" t="inlineStr"/>
       <c r="V11" s="5" t="inlineStr"/>
       <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -6136,6 +7152,8 @@
       <c r="U12" s="5" t="inlineStr"/>
       <c r="V12" s="5" t="inlineStr"/>
       <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6173,6 +7191,8 @@
       <c r="U13" s="5" t="inlineStr"/>
       <c r="V13" s="5" t="inlineStr"/>
       <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -6206,6 +7226,8 @@
       <c r="U14" s="5" t="inlineStr"/>
       <c r="V14" s="5" t="inlineStr"/>
       <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -6239,6 +7261,8 @@
       <c r="U15" s="5" t="inlineStr"/>
       <c r="V15" s="5" t="inlineStr"/>
       <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6272,6 +7296,8 @@
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
       <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6305,6 +7331,8 @@
       <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6338,6 +7366,8 @@
       <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -6371,6 +7401,8 @@
       <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -6404,6 +7436,8 @@
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
       <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -6437,6 +7471,8 @@
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
